--- a/appointment_forms/037_inquiry_form_for_readings--appointment_forms.xlsx
+++ b/appointment_forms/037_inquiry_form_for_readings--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>schedule_call_back</t>
+          <t>schedule_call_back_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Schedule Call Back</t>
+          <t>Schedule Call Back 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>schedule_call_back_other</t>
+          <t>schedule_call_back_other_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Schedule Call Back Other</t>
+          <t>Schedule Call Back Other 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>schedule_call_back_date</t>
+          <t>schedule_call_back_date_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Schedule Call Back Date</t>
+          <t>Schedule Call Back Date 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>schedule_call_back_time</t>
+          <t>schedule_call_back_time_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Schedule Call Back Time</t>
+          <t>Schedule Call Back Time 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'8:00_am'}</t>
+          <t>8:00_am</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '8:00 AM'}</t>
+          <t>8:00 AM</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'9:00_am'}</t>
+          <t>9:00_am</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '9:00 AM'}</t>
+          <t>9:00 AM</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'10:00_am'}</t>
+          <t>10:00_am</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '10:00 AM'}</t>
+          <t>10:00 AM</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'11:00_am'}</t>
+          <t>11:00_am</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '11:00 AM'}</t>
+          <t>11:00 AM</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'12:00_pm'}</t>
+          <t>12:00_pm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '12:00 PM'}</t>
+          <t>12:00 PM</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'1:00_pm'}</t>
+          <t>1:00_pm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': '1:00 PM'}</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'2:00_pm'}</t>
+          <t>2:00_pm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': '2:00 PM'}</t>
+          <t>2:00 PM</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'3:00_pm'}</t>
+          <t>3:00_pm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': '3:00 PM'}</t>
+          <t>3:00 PM</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'4:00_pm'}</t>
+          <t>4:00_pm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': '4:00 PM'}</t>
+          <t>4:00 PM</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'5:00_pm'}</t>
+          <t>5:00_pm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': '5:00 PM'}</t>
+          <t>5:00 PM</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'6:00_pm'}</t>
+          <t>6:00_pm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': '6:00 PM'}</t>
+          <t>6:00 PM</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'7:00_pm'}</t>
+          <t>7:00_pm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': '7:00 PM'}</t>
+          <t>7:00 PM</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'8:00_pm'}</t>
+          <t>8:00_pm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': '8:00 PM'}</t>
+          <t>8:00 PM</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'9:00_pm'}</t>
+          <t>9:00_pm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': '9:00 PM'}</t>
+          <t>9:00 PM</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'10:00_pm'}</t>
+          <t>10:00_pm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': '10:00 PM'}</t>
+          <t>10:00 PM</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'11:00_pm'}</t>
+          <t>11:00_pm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': '11:00 PM'}</t>
+          <t>11:00 PM</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'8:00_am_-_10:00_am'}</t>
+          <t>8:00_am_-_10:00_am</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '8:00 AM - 10:00 AM'}</t>
+          <t>8:00 AM - 10:00 AM</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'10:00_am_-_12:00_pm'}</t>
+          <t>10:00_am_-_12:00_pm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '10:00 AM - 12:00 PM'}</t>
+          <t>10:00 AM - 12:00 PM</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'12:00_pm_-_2:00_pm'}</t>
+          <t>12:00_pm_-_2:00_pm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '12:00 PM - 2:00 PM'}</t>
+          <t>12:00 PM - 2:00 PM</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'2:00_pm_-_4:00_pm'}</t>
+          <t>2:00_pm_-_4:00_pm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '2:00 PM - 4:00 PM'}</t>
+          <t>2:00 PM - 4:00 PM</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'4:00_pm_-_6:00_pm'}</t>
+          <t>4:00_pm_-_6:00_pm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '4:00 PM - 6:00 PM'}</t>
+          <t>4:00 PM - 6:00 PM</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'6:00_pm_-_8:00_pm'}</t>
+          <t>6:00_pm_-_8:00_pm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': '6:00 PM - 8:00 PM'}</t>
+          <t>6:00 PM - 8:00 PM</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'8:00_pm_-_10:00_pm'}</t>
+          <t>8:00_pm_-_10:00_pm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': '8:00 PM - 10:00 PM'}</t>
+          <t>8:00 PM - 10:00 PM</t>
         </is>
       </c>
     </row>
@@ -1606,46 +1606,46 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'10:00_pm_-_12:00_am'}</t>
+          <t>10:00_pm_-_12:00_am</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': '10:00 PM - 12:00 AM'}</t>
+          <t>10:00 PM - 12:00 AM</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>schedule_call_back_choices</t>
+          <t>schedule_call_back_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>schedule_call_back_choices</t>
+          <t>schedule_call_back_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
